--- a/artfynd/A 33891-2026 artfynd.xlsx
+++ b/artfynd/A 33891-2026 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>136042895</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136042897</v>
       </c>
       <c r="B7" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33891-2026 artfynd.xlsx
+++ b/artfynd/A 33891-2026 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>136042895</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136042897</v>
       </c>
       <c r="B7" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33891-2026 artfynd.xlsx
+++ b/artfynd/A 33891-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348997</v>
       </c>
       <c r="B2" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33891-2026 artfynd.xlsx
+++ b/artfynd/A 33891-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348997</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33891-2026 artfynd.xlsx
+++ b/artfynd/A 33891-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136348997</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
